--- a/docs/test/unit/NOUS-104/観点表_opportunityRunner.xlsx
+++ b/docs/test/unit/NOUS-104/観点表_opportunityRunner.xlsx
@@ -13,9 +13,9 @@
     <sheet name="対象概要" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'観点表'!$A$4:$Q$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'観点表'!$A$4:$Q$40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'観点表'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'テストデータ'!$A$4:$F$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'テストデータ'!$A$4:$F$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -846,7 +846,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>B5-T, B6-T, B7-T, B8-F, B9-F, B13-F, B14-F, B15-F, B16-F, B17-F, B25-F</t>
+          <t>B5-T, B6-T, B7-T, B8-F, B9-F, B13-F, B14-F, B15-F, B16-F, B17-F, B25-F, B2-T, B3-T</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>B10-F, B23-T, B4-T</t>
+          <t>B10-F, B23-T, B4-T, B18-F, B19-F, B20-F, B21-F, B22-F, B24-F</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>B18-T</t>
+          <t>B18-T, B24-F</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>B19-T</t>
+          <t>B19-T, B18-F, B24-F</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>B20-T, B4-T</t>
+          <t>B20-T, B4-T, B18-F, B19-F</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1292,7 +1292,7 @@
       <c r="Q13" s="7" t="inlineStr">
         <is>
           <t>既存テスト：実装時のテスト（NOUS-63）
-確認事項 3・4</t>
+確認事項 2、実施の手がかり</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>B22-T, B24-T</t>
+          <t>B22-T, B24-T, B18-F, B19-F, B20-F, B21-F, B22-F, B23-F</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1363,7 +1363,7 @@
       <c r="Q14" s="7" t="inlineStr">
         <is>
           <t>既存テスト：実装時のテスト（NOUS-63）
-確認事項 4</t>
+実施の手がかり</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>B20-T</t>
+          <t>B20-T, B18-F, B19-F</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>B20-T</t>
+          <t>B20-T, B18-F, B19-F</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1504,7 +1504,7 @@
       <c r="Q16" s="7" t="inlineStr">
         <is>
           <t>既存テスト：実装時のテスト（NOUS-83）
-確認事項 4</t>
+実施の手がかり</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>B10-T, B22-T</t>
+          <t>B10-T, B22-T, B18-F, B19-F, B20-F, B21-F</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>B10-T, B22-T</t>
+          <t>B10-T, B22-T, B18-F, B19-F, B20-F, B21-F</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>B21-T</t>
+          <t>B21-T, B18-F, B19-F, B20-F</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>B22-T, B4-T</t>
+          <t>B22-T, B4-T, B18-F, B19-F, B20-F, B21-F</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       <c r="Q26" s="7" t="inlineStr">
         <is>
           <t>既存テスト：なし
-確認事項 2。設計書に記載なし。実装の値</t>
+確認事項 1。設計書に記載なし。実装の値</t>
         </is>
       </c>
     </row>
@@ -2661,13 +2661,13 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>world_settings が無いとき ctx.settings の上限で待ちの後の停止を判定する</t>
+          <t>world_settings が無いとき ctx.settings の Neurons の上限で待ちの後の停止を判定する</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>前提：一時 DB（createTestDb）、FakeClock 2026-10-22T09:00:00.000Z、world_settings の無い世界
-入力：timeout、settings の runs 上限 1</t>
+          <t>前提：一時 DB（createTestDb）、FakeClock 2026-10-22T09:00:00.000Z、world_settings の無い世界、daily_usage neurons=100
+入力：timeout、settings の Neurons 上限 100・runs 上限 480</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -2689,7 +2689,7 @@
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_RUN-016 generateAndValidate は world_settings が無いとき ctx.settings の上限で待ちの後の停止を判定する</t>
+          <t>TC-UT_RUN-016 generateAndValidate は world_settings が無いとき ctx.settings の Neurons の上限で待ちの後の停止を判定する</t>
         </is>
       </c>
       <c r="N33" s="6" t="inlineStr">
@@ -2701,7 +2701,8 @@
       <c r="P33" s="6" t="inlineStr"/>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>既存テスト：なし</t>
+          <t>既存テスト：なし
+疑い 2 の決定により、上限の判定は Neurons で見る</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2793,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>正常系</t>
+          <t>異常系</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -2802,23 +2803,23 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>1 回目が不正な形式のとき、その呼び出し中に stopSignal が abort されていても再生成を 1 回呼ぶ</t>
+          <t>1 回目が不正な形式のとき、その呼び出し中に stopSignal が abort されていたら、再生成を呼ばずに cancelled（stopped）で閉じる</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
           <t>前提：一時 DB（createTestDb）、FakeClock 2026-10-22T09:00:00.000Z
-入力：呼び出し中に stopSignal を abort して不正な出力・post</t>
+入力：呼び出し中に stopSignal を abort して不正な出力</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>呼び出し 2 回、succeeded・post</t>
+          <t>呼び出し 1 回、cancelled・stopped</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>B10-T</t>
+          <t>B9-T, B10-T, B18-F, B19-F, B20-T</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
@@ -2830,7 +2831,7 @@
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_RUN-018 1 回目が不正な形式のとき、その呼び出し中に stopSignal が abort されていても再生成を 1 回呼ぶ</t>
+          <t>TC-UT_RUN-018 1 回目が不正な形式のとき、その呼び出し中に stopSignal が abort されていたら、再生成を呼ばずに cancelled（stopped）で閉じる</t>
         </is>
       </c>
       <c r="N35" s="6" t="inlineStr">
@@ -2843,7 +2844,8 @@
       <c r="Q35" s="7" t="inlineStr">
         <is>
           <t>既存テスト：なし
-確認事項 1。設計書に記載なし。実装の値</t>
+疑い：実装は再生成の前に stopSignal を見ず、再生成を呼ぶ（疑い 3）
+2026-10-26 Kouhei Tajima の決定：停止の後の再生成は待ちと同じく止める（AC-P06）</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2961,7 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>B19-T</t>
+          <t>B19-T, B18-F</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -2988,9 +2990,221 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>TC-UT_RUN-021</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>runOpportunity / generateAndValidate</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>異常系</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>状態遷移</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>1 回目が不正な形式で、再生成の前に世界が止まっていたら（shouldContinue が false）、再生成を呼ばずに cancelled（stopped）で閉じる</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>前提：一時 DB（createTestDb）、FakeClock 2026-10-22T09:00:00.000Z
+入力：1 回目の呼び出しの中で shouldContinue を false にして不正な出力</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>呼び出し 1 回、cancelled・stopped</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>B9-T, B10-T, B18-F, B19-F, B20-T</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>LLM の差し替え、shouldContinue</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr"/>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>TC-UT_RUN-021 1 回目が不正な形式で、再生成の前に世界が止まっていたら（shouldContinue が false）、再生成を呼ばずに cancelled（stopped）で閉じる</t>
+        </is>
+      </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="inlineStr"/>
+      <c r="P38" s="6" t="inlineStr"/>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>既存テスト：なし
+疑い：実装は再生成の前に shouldContinue を見ず、再生成を呼ぶ（疑い 3）
+2026-10-26 Kouhei Tajima の決定</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>TC-UT_RUN-022</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>createEvent</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>異常系</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>分岐網羅</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>世界が無ければ例外を投げ、生成イベントを作らない</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>前提：一時 DB（createTestDb）、FakeClock 2026-10-22T09:00:00.000Z
+入力：存在しない worldId</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>例外（World not found）、生成イベント 0 件</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>B2-F</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr"/>
+      <c r="L39" s="5" t="inlineStr"/>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>TC-UT_RUN-022 createEvent は世界が無ければ例外を投げ、生成イベントを作らない</t>
+        </is>
+      </c>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="inlineStr"/>
+      <c r="P39" s="6" t="inlineStr"/>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
+          <t>既存テスト：なし（runOpportunity は先に世界を確かめるので、この分岐は直接呼んだときだけ通る）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>TC-UT_RUN-023</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>createEvent</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>異常系</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>分岐網羅</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>world_settings が無ければ例外を投げ、生成イベントを作らない</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>前提：一時 DB（createTestDb）、FakeClock 2026-10-22T09:00:00.000Z、world_settings の無い世界
+入力：その世界の worldId</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>例外（World settings not found）、生成イベント 0 件</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>B2-T, B3-F</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>TC-UT_RUN-023 createEvent は world_settings が無ければ例外を投げ、生成イベントを作らない</t>
+        </is>
+      </c>
+      <c r="N40" s="6" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="O40" s="6" t="inlineStr"/>
+      <c r="P40" s="6" t="inlineStr"/>
+      <c r="Q40" s="7" t="inlineStr">
+        <is>
+          <t>既存テスト：なし（同上）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:Q37"/>
-  <conditionalFormatting sqref="A5:Q87">
+  <autoFilter ref="A4:Q40"/>
+  <conditionalFormatting sqref="A5:Q90">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$N5="NG"</formula>
     </cfRule>
@@ -3002,10 +3216,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N5:N87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N5:N90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,OK,NG,保留,対象外"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"正常系,異常系"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3057,7 +3271,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTA(観点表!$B$5:$B$87)</f>
+        <f>COUNTA(観点表!$B$5:$B$90)</f>
         <v/>
       </c>
     </row>
@@ -3068,7 +3282,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(観点表!$D$5:$D$87,"正常系")</f>
+        <f>COUNTIF(観点表!$D$5:$D$90,"正常系")</f>
         <v/>
       </c>
     </row>
@@ -3079,7 +3293,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(観点表!$D$5:$D$87,"異常系")</f>
+        <f>COUNTIF(観点表!$D$5:$D$90,"異常系")</f>
         <v/>
       </c>
     </row>
@@ -3099,7 +3313,7 @@
         </is>
       </c>
       <c r="B10" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$87,"エラー処理")</f>
+        <f>COUNTIF(観点表!$E$5:$E$90,"エラー処理")</f>
         <v/>
       </c>
     </row>
@@ -3110,7 +3324,7 @@
         </is>
       </c>
       <c r="B11" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$87,"分岐網羅")</f>
+        <f>COUNTIF(観点表!$E$5:$E$90,"分岐網羅")</f>
         <v/>
       </c>
     </row>
@@ -3121,7 +3335,7 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$87,"同値分割")</f>
+        <f>COUNTIF(観点表!$E$5:$E$90,"同値分割")</f>
         <v/>
       </c>
     </row>
@@ -3132,7 +3346,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$87,"境界値")</f>
+        <f>COUNTIF(観点表!$E$5:$E$90,"境界値")</f>
         <v/>
       </c>
     </row>
@@ -3143,7 +3357,7 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$87,"状態遷移")</f>
+        <f>COUNTIF(観点表!$E$5:$E$90,"状態遷移")</f>
         <v/>
       </c>
     </row>
@@ -3154,7 +3368,7 @@
         </is>
       </c>
       <c r="B15" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$87,"開発者テスト")</f>
+        <f>COUNTIF(観点表!$E$5:$E$90,"開発者テスト")</f>
         <v/>
       </c>
     </row>
@@ -3174,7 +3388,7 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIF(観点表!$K$5:$K$87,"?*")</f>
+        <f>COUNTIF(観点表!$K$5:$K$90,"?*")</f>
         <v/>
       </c>
     </row>
@@ -3205,7 +3419,7 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$87,"未実施")</f>
+        <f>COUNTIF(観点表!$N$5:$N$90,"未実施")</f>
         <v/>
       </c>
     </row>
@@ -3216,7 +3430,7 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$87,"OK")</f>
+        <f>COUNTIF(観点表!$N$5:$N$90,"OK")</f>
         <v/>
       </c>
     </row>
@@ -3227,7 +3441,7 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$87,"NG")</f>
+        <f>COUNTIF(観点表!$N$5:$N$90,"NG")</f>
         <v/>
       </c>
     </row>
@@ -3238,7 +3452,7 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$87,"保留")</f>
+        <f>COUNTIF(観点表!$N$5:$N$90,"保留")</f>
         <v/>
       </c>
     </row>
@@ -3249,7 +3463,7 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$87,"対象外")</f>
+        <f>COUNTIF(観点表!$N$5:$N$90,"対象外")</f>
         <v/>
       </c>
     </row>
@@ -3286,7 +3500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3911,7 +4125,7 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>world_settings が無いとき ctx.settings の上限で待ちの後の停止を判定する</t>
+          <t>world_settings が無いとき ctx.settings の Neurons の上限で待ちの後の停止を判定する</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -3951,7 +4165,7 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>1 回目が不正な形式のとき、その呼び出し中に stopSignal が abort されていても再生成を 1 回呼ぶ</t>
+          <t>1 回目が不正な形式のとき、その呼び出し中に stopSignal が abort されていたら、再生成を呼ばずに cancelled（stopped）で閉じる</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
@@ -4003,8 +4217,68 @@
       <c r="E37" s="13" t="inlineStr"/>
       <c r="F37" s="13" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>TC-UT_RUN-021</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>1 回目が不正な形式で、再生成の前に世界が止まっていたら（shouldContinue が false）、再生成を呼ばずに cancelled（stopped）で閉じる</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>未作成</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr"/>
+      <c r="E38" s="13" t="inlineStr"/>
+      <c r="F38" s="13" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>TC-UT_RUN-022</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>世界が無ければ例外を投げ、生成イベントを作らない</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>未作成</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr"/>
+      <c r="E39" s="13" t="inlineStr"/>
+      <c r="F39" s="13" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>TC-UT_RUN-023</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>world_settings が無ければ例外を投げ、生成イベントを作らない</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>未作成</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr"/>
+      <c r="E40" s="13" t="inlineStr"/>
+      <c r="F40" s="13" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F37"/>
+  <autoFilter ref="A4:F40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -4519,7 +4793,7 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>catch：想定外の例外（server_error）</t>
+          <t>catch：想定外の例外（server_error）。偽は B18〜B23 のどれかに当たったとき</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
@@ -4555,35 +4829,35 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>・疑い 1：不正な形式の試行は LLM が応答しており Neurons を消費しているが、トークン・Neurons を 0 で記録している。daily_usage.neurons が実際の消費より少なくなり、日次上限の判定が甘くなる。runOpportunity の通しでも、不正な形式の後に再生成で成功したとき daily_usage.neurons・生成イベントの neurons・戻り値の neurons に 1 回目の分が入らない。TC-UT_RUN-017 は設計どおりの期待結果で書いた（実施で NG になる見込み）。TC-NOUS63_DEV-18 は 1 回目の Neurons 0 を期待しており、疑いと食い違う</t>
+          <t>・疑い 1：不正な形式の試行は LLM が応答しており Neurons を消費しているが、トークン・Neurons を 0 で記録している。daily_usage.neurons が実際の消費より少なくなり、日次上限の判定が甘くなる。runOpportunity の通しでも、不正な形式の後に再生成で成功したとき daily_usage.neurons・生成イベントの neurons・戻り値の neurons に 1 回目の分が入らない。加算するのが仕様（2026-10-26 Kouhei Tajima の決定）。TC-UT_RUN-017 は仕様の期待結果で書いた（実施で NG の見込み）。TC-NOUS63_DEV-18 は 1 回目の Neurons 0 を期待しており、仕様と食い違う</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 1：不正な形式の後の再生成の前には shouldContinue・stopSignal を見ないため、一時停止・上限停止の指示の後でも再生成を 1 回呼ぶ（TC-UT_RUN-018 は実装の値）。1 回の呼び出しは最大 60 秒なので AC-P06（60 秒以内）は満たすが、待ちの打ち切りと同じく再生成も止めるかを決めてほしい</t>
+          <t>・疑い 3：一時停止・上限停止の後の再生成は、待ちと同じく止めるのが仕様（2026-10-26 Kouhei Tajima の決定）。実装は不正な形式の後の再生成の前に shouldContinue・stopSignal を見ないため、止めた後でも再生成を 1 回呼ぶ。TC-UT_RUN-018（stopSignal）・TC-UT_RUN-021（shouldContinue）は仕様の期待結果（再生成を呼ばずに cancelled・stopped で閉じる）で書いた（実施で NG の見込み）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 2：00:00 UTC をまたいで再試行したとき、試行は呼んだ日の daily_usage に、指標は生成イベントの日の daily_metrics に入る（TC-UT_RUN-009）。設計書に記載がないため実装の値で書いた。Cloudflare の日次の枠が 00:00 UTC で切り替わるのとは合っている</t>
+          <t>・確認事項 1：00:00 UTC をまたいで再試行したとき、試行は呼んだ日の daily_usage に、指標は生成イベントの日の daily_metrics に入る（TC-UT_RUN-009）。設計書に記載がないため実装の値で書いた。Cloudflare の日次の枠が 00:00 UTC で切り替わるのとは合っている</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 3：TC-NOUS63_DEV-23 は名前に「イベント作成後の AgentNotActiveError」とあるが、実際には closeCancelled などを直接呼んでおり、その経路は通っていない。TC-UT_RUN-006 で補った</t>
+          <t>・確認事項 2：TC-NOUS63_DEV-23 は名前に「イベント作成後の AgentNotActiveError」とあるが、実際には closeCancelled などを直接呼んでおり、その経路は通っていない。TC-UT_RUN-006 で補った</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 4：TC-NOUS63_DEV-23・24、TC-NOUS83_DEV-07 は runOpportunity を呼んだ直後に clock.advance するため、sleep が張られる前に時刻が進む可能性がある。実施のときに落ちたら、テストの書き方の問題として切り分ける</t>
+          <t>・実施の手がかり：TC-NOUS63_DEV-23・24、TC-NOUS83_DEV-07 は runOpportunity を呼んだ直後に clock.advance するため、sleep が張られる前に時刻が進む可能性がある。実施のときに落ちたら、まずテストの書き方の問題として切り分ける</t>
         </is>
       </c>
     </row>
